--- a/data/trans_dic/IP1002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen bornquitis crónica</t>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,45</t>
+          <t>0,42; 4,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,07</t>
+          <t>1,33; 6,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,4</t>
+          <t>0,35; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,59</t>
+          <t>0,54; 5,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,89</t>
+          <t>1,35; 6,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,09</t>
+          <t>2,09; 8,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,63</t>
+          <t>0,81; 3,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,98</t>
+          <t>1,71; 5,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,82</t>
+          <t>1,34; 4,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,15</t>
+          <t>0,56; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,62</t>
+          <t>0,6; 3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,64</t>
+          <t>1,24; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,21</t>
+          <t>1,19; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,73</t>
+          <t>0,34; 3,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,93</t>
+          <t>1,94; 5,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,51</t>
+          <t>0,26; 2,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,1</t>
+          <t>0,99; 6,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,55</t>
+          <t>0,73; 2,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,02</t>
+          <t>1,62; 4,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,9</t>
+          <t>0,92; 2,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,12</t>
+          <t>1,46; 4,88</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,6</t>
+          <t>0,98; 5,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,88</t>
+          <t>0,47; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,52</t>
+          <t>0,82; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,19</t>
+          <t>0,52; 3,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,23</t>
+          <t>0,65; 3,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,41</t>
+          <t>0,42; 2,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,62</t>
+          <t>0,32; 2,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,98</t>
+          <t>0,29; 3,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,64</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,7</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,2</t>
+          <t>0,73; 2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,5</t>
+          <t>0,84; 2,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,84</t>
+          <t>0,57; 1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,33</t>
+          <t>0,7; 2,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,12</t>
+          <t>0,61; 1,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,23</t>
+          <t>0,8; 2,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,53</t>
+          <t>0,77; 2,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,85; 1,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,67</t>
+          <t>1,45; 2,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,77</t>
+          <t>0,84; 1,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,01</t>
+          <t>0,81; 1,99</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>445; 4623</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1951; 9423</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>459; 4299</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4227</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>656; 6582</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1952; 8783</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2589; 10320</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1844; 8576</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4985; 14609</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3423; 11683</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4390</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3745</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9496</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4947</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13241</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7986</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1425; 8380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1407; 8138</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2606; 10159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1888; 9225</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>872; 7746</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5180; 15562</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>681; 5996</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1812; 11898</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3692; 12720</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8129; 20390</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4304; 13645</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5001; 16699</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1674</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1250; 7053</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5037</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>806; 7591</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4118</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7032</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4645</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5104</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1408; 8108</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2046; 10208</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5022</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1612; 9312</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4034</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2643</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3518</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3349</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4455</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>664; 5415</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4827</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4566</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>897; 11523</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>679; 6068</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5892</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5358</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1337; 11285</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18105</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4955; 14993</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5958; 17024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3992; 12658</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4649; 14870</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4393; 13975</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12635; 27606</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5957; 16412</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5837; 18656</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11998; 27440</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>21118; 38755</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12131; 25866</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>11584; 28318</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Edad-trans_dic.xlsx
@@ -722,32 +722,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,44</t>
+          <t>1,62; 6,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,27</t>
+          <t>0,34; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,42</t>
+          <t>0,54; 5,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,08</t>
+          <t>0,98; 6,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,31</t>
+          <t>2,06; 7,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,77</t>
+          <t>0,78; 3,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,02</t>
+          <t>1,59; 5,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,57</t>
+          <t>1,43; 4,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,31</t>
+          <t>0,69; 3,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,47</t>
+          <t>0,61; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,83</t>
+          <t>0,95; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,79</t>
+          <t>1,19; 5,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,05</t>
+          <t>0,34; 2,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,83</t>
+          <t>1,89; 5,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,32</t>
+          <t>0,25; 2,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,52</t>
+          <t>0,99; 6,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,51</t>
+          <t>0,68; 2,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,07</t>
+          <t>1,61; 4,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,91</t>
+          <t>0,94; 3,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,88</t>
+          <t>1,51; 5,13</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,53</t>
+          <t>0,91; 5,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,39</t>
+          <t>0,45; 4,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,43</t>
+          <t>0,82; 4,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,01</t>
+          <t>0,54; 3,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,26</t>
+          <t>0,64; 2,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,42</t>
+          <t>0,43; 2,5</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,63</t>
+          <t>0,32; 2,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,77</t>
+          <t>0,28; 3,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,52</t>
+          <t>0,17; 1,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,15; 1,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,2</t>
+          <t>0,82; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,91; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,8</t>
+          <t>0,59; 1,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,23</t>
+          <t>0,76; 2,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,93</t>
+          <t>0,67; 2,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,69</t>
+          <t>1,55; 3,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,2</t>
+          <t>0,82; 2,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,45</t>
+          <t>0,75; 2,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,95</t>
+          <t>0,88; 1,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,41; 2,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,78</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,99</t>
+          <t>0,91; 2,05</t>
         </is>
       </c>
     </row>
@@ -1645,37 +1645,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>445; 4623</t>
+          <t>447; 4613</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1951; 9423</t>
+          <t>2366; 9450</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>459; 4299</t>
+          <t>450; 4292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>0; 4294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>656; 6582</t>
+          <t>657; 6392</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1952; 8783</t>
+          <t>1411; 8753</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2589; 10320</t>
+          <t>2559; 9451</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1844; 8576</t>
+          <t>1783; 8419</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4985; 14609</t>
+          <t>4629; 14597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3423; 11683</t>
+          <t>3660; 11883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4390</t>
+          <t>0; 4542</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1425; 8380</t>
+          <t>1756; 8359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1407; 8138</t>
+          <t>1419; 8884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2606; 10159</t>
+          <t>2006; 9982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1888; 9225</t>
+          <t>1897; 9279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>872; 7746</t>
+          <t>866; 7459</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5180; 15562</t>
+          <t>5058; 15352</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>681; 5996</t>
+          <t>640; 6536</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1812; 11898</t>
+          <t>1804; 11413</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3692; 12720</t>
+          <t>3438; 12739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8129; 20390</t>
+          <t>8081; 20763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4304; 13645</t>
+          <t>4401; 14046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5001; 16699</t>
+          <t>5152; 17541</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1250; 7053</t>
+          <t>1167; 7234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5037</t>
+          <t>0; 5068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,47 +2076,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>806; 7591</t>
+          <t>786; 7417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1301; 7032</t>
+          <t>1297; 7337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4772</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5104</t>
+          <t>0; 5086</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1408; 8108</t>
+          <t>1440; 8996</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2046; 10208</t>
+          <t>1993; 9033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5022</t>
+          <t>0; 4963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1612; 9312</t>
+          <t>1646; 9609</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2269,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4455</t>
+          <t>0; 3913</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2289,42 +2289,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>664; 5415</t>
+          <t>667; 5934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4827</t>
+          <t>0; 4972</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4566</t>
+          <t>0; 4207</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>897; 11523</t>
+          <t>850; 10508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>679; 6068</t>
+          <t>679; 6631</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5892</t>
+          <t>0; 5261</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1337; 11285</t>
+          <t>879; 10193</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4955; 14993</t>
+          <t>5571; 15385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5958; 17024</t>
+          <t>6422; 17518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3992; 12658</t>
+          <t>4151; 13589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4649; 14870</t>
+          <t>5037; 15481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4393; 13975</t>
+          <t>4825; 14763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12635; 27606</t>
+          <t>11606; 26197</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5957; 16412</t>
+          <t>6091; 16307</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5837; 18656</t>
+          <t>5675; 19366</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11998; 27440</t>
+          <t>12396; 25768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21118; 38755</t>
+          <t>20506; 37721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12131; 25866</t>
+          <t>11636; 25341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11584; 28318</t>
+          <t>12932; 29264</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,35</t>
+          <t>0,54; 5,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,46</t>
+          <t>1,21; 5,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,26</t>
+          <t>1,73; 8,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,27</t>
+          <t>0,42; 4,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,06</t>
+          <t>1,6; 6,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,61</t>
+          <t>0,34; 3,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,7</t>
+          <t>0,81; 3,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,02</t>
+          <t>1,71; 4,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,65</t>
+          <t>1,39; 4,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,3</t>
+          <t>0,29; 2,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,79</t>
+          <t>1,85; 5,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,74</t>
+          <t>0,27; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,83</t>
+          <t>0,83; 5,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,94</t>
+          <t>0,56; 3,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,75</t>
+          <t>0,63; 3,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,53</t>
+          <t>1,12; 4,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,25</t>
+          <t>1,27; 6,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,51</t>
+          <t>0,7; 2,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,14</t>
+          <t>1,63; 4,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,0</t>
+          <t>0,92; 2,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,13</t>
+          <t>1,5; 4,89</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,67</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,81; 4,52</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,83</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,91; 5,6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,27</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 4,29</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,85</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 4,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,53</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,5; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,34</t>
+          <t>0,52; 3,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,88</t>
+          <t>0,65; 3,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,5</t>
+          <t>0,46; 2,58</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,32; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>0,33; 3,29</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,59</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,68</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,85</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 2,88</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,79</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,42</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 3,44</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,66</t>
+          <t>0,17; 1,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,75</t>
+          <t>0,16; 1,94</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,26</t>
+          <t>0,58; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,48</t>
+          <t>1,52; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,93</t>
+          <t>0,81; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,33</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,04</t>
+          <t>0,76; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,5</t>
+          <t>0,91; 2,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,19</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,54</t>
+          <t>0,72; 2,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,84</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,59</t>
+          <t>1,45; 2,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,85; 1,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,05</t>
+          <t>0,89; 2,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1668</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4929</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1577</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5330</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1307</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>447; 4613</t>
+          <t>650; 6789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2366; 9450</t>
+          <t>1752; 8512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>450; 4292</t>
+          <t>2149; 10048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>657; 6392</t>
+          <t>442; 4728</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1411; 8753</t>
+          <t>2337; 8884</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2559; 9451</t>
+          <t>450; 4482</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4479</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1783; 8419</t>
+          <t>1846; 8251</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4629; 14597</t>
+          <t>4980; 14472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3660; 11883</t>
+          <t>3551; 12332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4542</t>
+          <t>0; 4493</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4008</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3745</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5366</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4569</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9496</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2620</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>8356</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1756; 8359</t>
+          <t>728; 6940</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1419; 8884</t>
+          <t>4939; 15841</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2006; 9982</t>
+          <t>691; 6475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1897; 9279</t>
+          <t>1301; 8864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>866; 7459</t>
+          <t>1411; 7979</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5058; 15352</t>
+          <t>1485; 8483</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640; 6536</t>
+          <t>2368; 9757</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1804; 11413</t>
+          <t>1844; 9819</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3438; 12739</t>
+          <t>3531; 12932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8081; 20763</t>
+          <t>8160; 20157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4401; 14046</t>
+          <t>4327; 13605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5152; 17541</t>
+          <t>4536; 14811</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1634</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3292</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1438</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2952</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1363</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1674</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4586</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1167; 7234</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>1292; 7173</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4714</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5629</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1167; 7148</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5065</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>786; 7417</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4039</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1297; 7337</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4772</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>876; 7124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1440; 8996</t>
+          <t>1409; 8591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1993; 9033</t>
+          <t>2040; 10137</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1646; 9609</t>
+          <t>1712; 9649</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,44 +2201,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4034</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2643</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4255</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>665; 5394</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4040</t>
+          <t>0; 4761</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3913</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>961; 9635</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4599</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3212</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>667; 5934</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4972</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4207</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>850; 10508</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>679; 6631</t>
+          <t>676; 6571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5261</t>
+          <t>0; 6171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4650</t>
+          <t>0; 5389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>879; 10193</t>
+          <t>904; 10663</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5571; 15385</t>
+          <t>4177; 15357</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6422; 17518</t>
+          <t>11363; 25718</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4151; 13589</t>
+          <t>6040; 16584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5037; 15481</t>
+          <t>5041; 17203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4825; 14763</t>
+          <t>5199; 14993</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11606; 26197</t>
+          <t>6421; 17680</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6091; 16307</t>
+          <t>3827; 12962</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5675; 19366</t>
+          <t>4524; 15265</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12396; 25768</t>
+          <t>12002; 25622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20506; 37721</t>
+          <t>21163; 38840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11636; 25341</t>
+          <t>12253; 25723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12932; 29264</t>
+          <t>11820; 27210</t>
         </is>
       </c>
     </row>
